--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ценовая лестница" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pro 14 юниты" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pro 15 юниты" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прочие юниты" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ultra (все версии)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лоты без паспортов" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Динамика" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фокус 6600H-6800H-Ultra" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Движение юнитов" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Движение все Pro" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статус сбора" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Покрытие" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Словарь обозначений" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Методика" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ценовая лестница" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pro 14 юниты" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pro 15 юниты" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Прочие юниты" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ultra (все версии)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Лоты без паспортов" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Динамика" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Фокус 6600H-6800H-Ultra" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Движение юнитов" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Движение все Pro" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Статус сбора" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Покрытие" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Словарь обозначений" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Методика" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pro 14 юниты'!$A$4:$M$33</definedName>
@@ -268,13 +268,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -298,7 +298,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -347,7 +347,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -362,9 +362,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1385,7 +1385,7 @@
         <v>32617</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>25337</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>32617</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:10:04+07:00</t>
+          <t>2026-10-25T21:20:05+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:20:05+07:00</t>
+          <t>2026-10-25T22:46:17+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T21:20:14+07:00</t>
+          <t>2026-10-25T23:06:26+07:00</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>3 / 2 / 1</t>
+          <t>1 / 1 / 1</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T22:46:17+07:00</t>
+          <t>2026-10-25T23:49:48+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T23:06:26+07:00</t>
+          <t>2026-10-25T23:57:13+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T23:49:48+07:00</t>
+          <t>2026-10-26T01:15:28+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-25T23:57:13+07:00</t>
+          <t>2026-10-26T01:17:17+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T01:15:28+07:00</t>
+          <t>2026-10-26T02:43:47+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T01:17:17+07:00</t>
+          <t>2026-10-26T02:51:25+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T02:43:47+07:00</t>
+          <t>2026-10-26T03:44:17+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T02:51:25+07:00</t>
+          <t>2026-10-26T04:11:17+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T03:44:17+07:00</t>
+          <t>2026-10-26T05:12:51+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T04:11:17+07:00</t>
+          <t>2026-10-26T05:15:04+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T05:12:51+07:00</t>
+          <t>2026-10-26T06:40:35+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T05:15:04+07:00</t>
+          <t>2026-10-26T06:42:46+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T06:40:35+07:00</t>
+          <t>2026-10-26T08:16:47+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T06:42:46+07:00</t>
+          <t>2026-10-26T08:20:01+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T08:16:47+07:00</t>
+          <t>2026-10-26T09:31:09+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T08:20:01+07:00</t>
+          <t>2026-10-26T09:59:47+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T09:31:09+07:00</t>
+          <t>2026-10-26T10:52:32+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T09:59:47+07:00</t>
+          <t>2026-10-26T11:10:56+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T10:52:32+07:00</t>
+          <t>2026-10-26T12:13:12+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T11:10:56+07:00</t>
+          <t>2026-10-26T12:25:53+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1493,7 +1493,7 @@
         <v>42887</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>49127</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>49517</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>50557</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>52767</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>53027</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>62127</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>62127</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>53027</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>55757</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>58877</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>70577</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>72007</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>72397</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>73177</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>24947</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>24947</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>27027</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>27027</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>28327</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>29237</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>32227</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>25337</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>42887</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>49127</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>49517</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>50557</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>52767</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>53027</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>62127</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>62127</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>53027</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>55757</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>58877</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>70577</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>72007</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>72397</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>73177</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T12:13:12+07:00</t>
+          <t>2026-10-26T13:27:09+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T12:25:53+07:00</t>
+          <t>2026-10-26T13:51:23+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T13:27:09+07:00</t>
+          <t>2026-10-26T15:22:32+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T13:51:23+07:00</t>
+          <t>2026-10-26T15:30:56+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T15:22:32+07:00</t>
+          <t>2026-10-26T17:19:27+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T15:30:56+07:00</t>
+          <t>2026-10-26T17:21:00+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1421,7 +1421,7 @@
         <v>32227</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>35477</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>25207</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>25727</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>26247</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>26637</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>26767</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>27157</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>27417</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>28197</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>29887</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>27807</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>30407</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>30667</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>31057</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>31317</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>31317</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>32227</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>32227</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>34177</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>36387</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>29627</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>29887</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>30017</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>40677</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>26767</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>27807</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>27807</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>27937</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>27937</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>27937</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>30667</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>30667</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>28847</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>30927</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>32227</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>35477</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T17:19:27+07:00</t>
+          <t>2026-10-26T18:00:32+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T17:21:00+07:00</t>
+          <t>2026-10-26T19:00:41+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T18:00:32+07:00</t>
+          <t>2026-10-26T20:33:54+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T19:00:41+07:00</t>
+          <t>2026-10-26T21:34:09+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1385,7 +1385,7 @@
         <v>32617</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>25337</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>32617</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T20:33:54+07:00</t>
+          <t>2026-10-26T23:16:06+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T21:34:09+07:00</t>
+          <t>2026-10-26T23:18:15+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:16:06+07:00</t>
+          <t>2026-10-27T00:51:07+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-26T23:18:15+07:00</t>
+          <t>2026-10-27T01:00:37+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T00:51:07+07:00</t>
+          <t>2026-10-27T02:21:53+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T01:00:37+07:00</t>
+          <t>2026-10-27T02:27:38+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T02:21:53+07:00</t>
+          <t>2026-10-27T03:51:22+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T02:27:38+07:00</t>
+          <t>2026-10-27T04:09:23+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T03:51:22+07:00</t>
+          <t>2026-10-27T05:08:09+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T04:09:23+07:00</t>
+          <t>2026-10-27T05:22:13+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T05:08:09+07:00</t>
+          <t>2026-10-27T06:50:03+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T05:22:13+07:00</t>
+          <t>2026-10-27T06:50:16+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T06:50:03+07:00</t>
+          <t>2026-10-27T07:20:50+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T06:50:16+07:00</t>
+          <t>2026-10-27T08:21:02+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T07:20:50+07:00</t>
+          <t>2026-10-27T09:12:15+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T08:21:02+07:00</t>
+          <t>2026-10-27T09:21:21+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:12:15+07:00</t>
+          <t>2026-10-27T10:22:52+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:21:21+07:00</t>
+          <t>2026-10-27T10:49:40+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T10:22:52+07:00</t>
+          <t>2026-10-27T11:49:37+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T10:49:40+07:00</t>
+          <t>2026-10-27T12:12:05+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -2874,7 +2874,7 @@
         <v>24947</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>24947</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>27027</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>29237</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T11:49:37+07:00</t>
+          <t>2026-10-27T13:09:38+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T12:12:05+07:00</t>
+          <t>2026-10-27T13:23:30+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1493,7 +1493,7 @@
         <v>42887</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>49127</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>49517</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>50557</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>52767</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>53027</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>62127</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>62127</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>53027</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>55757</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>58877</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>70577</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>72007</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>72397</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>73177</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>27027</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>28327</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>32227</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>25337</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>42887</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>49127</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>49517</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>50557</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>52767</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>53027</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>62127</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>62127</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>53027</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>55757</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>58877</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>70577</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>72007</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>72397</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>73177</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T13:09:38+07:00</t>
+          <t>2026-10-27T14:58:49+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T13:23:30+07:00</t>
+          <t>2026-10-27T15:03:15+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T14:58:49+07:00</t>
+          <t>2026-10-27T16:17:34+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T15:03:15+07:00</t>
+          <t>2026-10-27T16:36:14+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T16:17:34+07:00</t>
+          <t>2026-10-27T17:32:41+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T16:36:14+07:00</t>
+          <t>2026-10-27T17:58:44+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T17:32:41+07:00</t>
+          <t>2026-10-27T18:50:37+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T17:58:44+07:00</t>
+          <t>2026-10-27T19:14:16+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1421,7 +1421,7 @@
         <v>32227</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>35477</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>25207</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>25727</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>26247</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>26637</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>26767</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>27157</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>27417</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>28197</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>29887</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>27807</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>30407</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>30667</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>31057</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>31317</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>31317</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>32227</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>32227</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>34177</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>36387</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>29627</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>29887</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>30017</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>40677</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>26767</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>27807</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>27807</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>27937</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>27937</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>27937</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>30667</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>30667</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>28847</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>30927</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>32227</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>35477</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T18:50:37+07:00</t>
+          <t>2026-10-27T19:28:23+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T19:14:16+07:00</t>
+          <t>2026-10-27T20:28:33+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T19:28:23+07:00</t>
+          <t>2026-10-27T21:24:49+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T20:28:33+07:00</t>
+          <t>2026-10-27T21:29:05+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1385,7 +1385,7 @@
         <v>32617</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>25337</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>32617</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T21:24:49+07:00</t>
+          <t>2026-10-27T23:23:26+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T21:29:05+07:00</t>
+          <t>2026-10-27T23:23:50+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:23:26+07:00</t>
+          <t>2026-10-28T01:17:03+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:23:50+07:00</t>
+          <t>2026-10-28T01:22:21+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T01:17:03+07:00</t>
+          <t>2026-10-28T02:53:05+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T01:22:21+07:00</t>
+          <t>2026-10-28T03:02:27+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T02:53:05+07:00</t>
+          <t>2026-10-28T04:11:17+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T03:02:27+07:00</t>
+          <t>2026-10-28T04:26:59+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T04:11:17+07:00</t>
+          <t>2026-10-28T05:25:52+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T04:26:59+07:00</t>
+          <t>2026-10-28T05:50:13+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T05:25:52+07:00</t>
+          <t>2026-10-28T06:44:59+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T05:50:13+07:00</t>
+          <t>2026-10-28T07:08:53+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T06:44:59+07:00</t>
+          <t>2026-10-28T07:28:04+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T07:08:53+07:00</t>
+          <t>2026-10-28T08:28:17+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T07:28:04+07:00</t>
+          <t>2026-10-28T09:20:20+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T08:28:17+07:00</t>
+          <t>2026-10-28T09:33:40+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T09:20:20+07:00</t>
+          <t>2026-10-28T11:04:50+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T09:33:40+07:00</t>
+          <t>2026-10-28T11:19:32+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T11:04:50+07:00</t>
+          <t>2026-10-28T12:37:15+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T11:19:32+07:00</t>
+          <t>2026-10-28T12:59:26+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1493,7 +1493,7 @@
         <v>42887</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>49127</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>49517</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>50557</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>52767</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>53027</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>53027</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>55757</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>58877</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>24947</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>24947</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>27027</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>29237</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>42887</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>49127</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>49517</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>50557</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>52767</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>53027</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>53027</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>55757</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>58877</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T12:37:15+07:00</t>
+          <t>2026-10-28T13:16:12+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T12:59:26+07:00</t>
+          <t>2026-10-28T14:16:23+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1709,7 +1709,7 @@
         <v>62127</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>62127</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>70577</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>72007</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>72397</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>73177</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>27027</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>28327</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>32227</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>25337</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>62127</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>62127</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>70577</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>72007</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>72397</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>73177</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T13:16:12+07:00</t>
+          <t>2026-10-28T15:13:20+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T14:16:23+07:00</t>
+          <t>2026-10-28T15:18:21+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T15:13:20+07:00</t>
+          <t>2026-10-28T17:01:49+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T15:18:21+07:00</t>
+          <t>2026-10-28T17:03:50+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T17:01:49+07:00</t>
+          <t>2026-10-28T18:35:28+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T17:03:50+07:00</t>
+          <t>2026-10-28T18:58:37+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1421,7 +1421,7 @@
         <v>32227</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>35477</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>25207</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>25727</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>26247</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>26637</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>26767</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>27157</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>27417</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>28197</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>29887</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>27807</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>30407</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>30667</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>31057</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>31317</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>31317</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>32227</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>32227</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>34177</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>36387</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>29627</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>29887</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>30017</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>40677</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>26767</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>27807</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>27807</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>27937</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>27937</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>27937</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>30667</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>30667</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>28847</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>30927</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>32227</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>35477</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T18:35:28+07:00</t>
+          <t>2026-10-28T20:16:14+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T18:58:37+07:00</t>
+          <t>2026-10-28T20:16:35+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1385,7 +1385,7 @@
         <v>32617</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>25337</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>32617</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T20:16:14+07:00</t>
+          <t>2026-10-28T22:07:14+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T20:16:35+07:00</t>
+          <t>2026-10-28T22:13:13+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T22:07:14+07:00</t>
+          <t>2026-10-29T00:03:42+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-28T22:13:13+07:00</t>
+          <t>2026-10-29T00:04:57+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:03:42+07:00</t>
+          <t>2026-10-29T01:36:32+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T00:04:57+07:00</t>
+          <t>2026-10-29T01:58:04+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T01:36:32+07:00</t>
+          <t>2026-10-29T03:16:58+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T01:58:04+07:00</t>
+          <t>2026-10-29T03:27:25+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T03:16:58+07:00</t>
+          <t>2026-10-29T04:33:19+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T03:27:25+07:00</t>
+          <t>2026-10-29T04:59:19+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T04:33:19+07:00</t>
+          <t>2026-10-29T05:52:56+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T04:59:19+07:00</t>
+          <t>2026-10-29T06:15:16+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T05:52:56+07:00</t>
+          <t>2026-10-29T07:08:06+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T06:15:16+07:00</t>
+          <t>2026-10-29T07:24:43+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T07:08:06+07:00</t>
+          <t>2026-10-29T09:07:15+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T07:24:43+07:00</t>
+          <t>2026-10-29T09:14:54+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T09:07:15+07:00</t>
+          <t>2026-10-29T10:43:23+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T09:14:54+07:00</t>
+          <t>2026-10-29T11:00:17+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T10:43:23+07:00</t>
+          <t>2026-10-29T12:19:59+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T11:00:17+07:00</t>
+          <t>2026-10-29T12:35:10+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1493,7 +1493,7 @@
         <v>42887</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>49127</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>49517</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>50557</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>52767</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>53027</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>53027</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>55757</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>58877</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>24947</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>24947</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>27027</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>29237</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>42887</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>49127</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>49517</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>50557</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>52767</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>53027</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>53027</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>55757</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>58877</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T12:19:59+07:00</t>
+          <t>2026-10-29T13:02:00+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T12:35:10+07:00</t>
+          <t>2026-10-29T14:02:10+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1709,7 +1709,7 @@
         <v>62127</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>62127</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>70577</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>72007</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>72397</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>73177</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>27027</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>28327</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>32227</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>25337</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>62127</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>62127</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>70577</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>72007</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>72397</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>73177</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T13:02:00+07:00</t>
+          <t>2026-10-29T15:14:17+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T14:02:10+07:00</t>
+          <t>2026-10-29T15:16:04+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T15:14:17+07:00</t>
+          <t>2026-10-29T17:03:33+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T15:16:04+07:00</t>
+          <t>2026-10-29T17:05:46+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T17:03:33+07:00</t>
+          <t>2026-10-29T18:39:07+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T17:05:46+07:00</t>
+          <t>2026-10-29T19:00:11+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1421,7 +1421,7 @@
         <v>32227</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>35477</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>25207</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>25727</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>26247</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>26637</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>26767</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>27157</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>27417</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>28197</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>29887</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>27807</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>30407</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>30667</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>31057</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>31317</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>31317</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>32227</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>32227</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>34177</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>36387</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>29627</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>29887</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>30017</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>40677</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>26767</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>27807</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>27807</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>27937</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>27937</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>27937</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>30667</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>30667</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>28847</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>30927</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>32227</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>35477</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T18:39:07+07:00</t>
+          <t>2026-10-29T19:18:46+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T19:00:11+07:00</t>
+          <t>2026-10-29T20:18:55+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T19:18:46+07:00</t>
+          <t>2026-10-29T20:23:33+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T20:18:55+07:00</t>
+          <t>2026-10-29T21:23:43+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1385,7 +1385,7 @@
         <v>32617</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>25337</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>32617</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T20:23:33+07:00</t>
+          <t>2026-10-29T22:27:08+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T21:23:43+07:00</t>
+          <t>2026-10-29T22:28:01+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T22:27:08+07:00</t>
+          <t>2026-10-30T00:25:53+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-29T22:28:01+07:00</t>
+          <t>2026-10-30T00:28:05+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:25:53+07:00</t>
+          <t>2026-10-30T02:16:37+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:28:05+07:00</t>
+          <t>2026-10-30T02:20:03+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T02:16:37+07:00</t>
+          <t>2026-10-30T03:57:51+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T02:20:03+07:00</t>
+          <t>2026-10-30T04:01:54+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T03:57:51+07:00</t>
+          <t>2026-10-30T05:16:05+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T04:01:54+07:00</t>
+          <t>2026-10-30T05:32:36+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T05:16:05+07:00</t>
+          <t>2026-10-30T06:26:19+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T05:32:36+07:00</t>
+          <t>2026-10-30T06:56:29+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T06:26:19+07:00</t>
+          <t>2026-10-30T07:08:55+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T06:56:29+07:00</t>
+          <t>2026-10-30T08:09:05+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T07:08:55+07:00</t>
+          <t>2026-10-30T09:10:49+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T08:09:05+07:00</t>
+          <t>2026-10-30T09:18:28+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T09:10:49+07:00</t>
+          <t>2026-10-30T11:01:27+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T09:18:28+07:00</t>
+          <t>2026-10-30T11:01:46+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -2874,7 +2874,7 @@
         <v>24947</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>24947</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>27027</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>29237</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T11:01:27+07:00</t>
+          <t>2026-10-30T12:41:25+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T11:01:46+07:00</t>
+          <t>2026-10-30T13:00:09+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1493,7 +1493,7 @@
         <v>42887</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>49127</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>49517</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>50557</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>52767</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>53027</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>62127</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>62127</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>53027</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>55757</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>58877</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>70577</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>72007</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>72397</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>73177</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>27027</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>28327</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>32227</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>25337</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>42887</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>49127</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>49517</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>50557</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>52767</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>53027</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>62127</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>62127</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>53027</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>55757</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>58877</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>70577</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>72007</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>72397</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>73177</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T12:41:25+07:00</t>
+          <t>2026-10-30T13:33:10+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T13:00:09+07:00</t>
+          <t>2026-10-30T14:33:23+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T13:33:10+07:00</t>
+          <t>2026-10-30T15:28:41+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T14:33:23+07:00</t>
+          <t>2026-10-30T15:39:08+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T15:28:41+07:00</t>
+          <t>2026-10-30T17:24:50+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T15:39:08+07:00</t>
+          <t>2026-10-30T17:26:23+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1457,7 +1457,7 @@
         <v>35477</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>31317</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>32227</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>35477</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T17:24:50+07:00</t>
+          <t>2026-10-30T18:56:40+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T17:26:23+07:00</t>
+          <t>2026-10-30T19:16:07+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1421,7 +1421,7 @@
         <v>32227</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>25207</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>25727</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>26247</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>26637</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>26767</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>27157</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>27417</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>28197</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>29887</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>27807</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>30407</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>30667</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>31057</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>31317</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>32227</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>34177</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>36387</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>29627</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>29887</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>30017</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>40677</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>26767</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>27807</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>27807</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>27937</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>27937</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>27937</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>30667</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>30667</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>28847</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>30927</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>32227</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T18:56:40+07:00</t>
+          <t>2026-10-30T19:36:33+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T19:16:07+07:00</t>
+          <t>2026-10-30T20:36:44+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T19:36:33+07:00</t>
+          <t>2026-10-30T21:32:48+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T20:36:44+07:00</t>
+          <t>2026-10-30T21:38:36+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1385,7 +1385,7 @@
         <v>32617</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>25337</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>32617</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T21:32:48+07:00</t>
+          <t>2026-10-30T23:24:29+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T21:38:36+07:00</t>
+          <t>2026-10-30T23:25:31+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T23:24:29+07:00</t>
+          <t>2026-10-31T01:15:19+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-30T23:25:31+07:00</t>
+          <t>2026-10-31T01:20:59+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T01:15:19+07:00</t>
+          <t>2026-10-31T02:56:45+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T01:20:59+07:00</t>
+          <t>2026-10-31T03:00:36+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T02:56:45+07:00</t>
+          <t>2026-10-31T04:14:34+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T03:00:36+07:00</t>
+          <t>2026-10-31T04:28:18+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T04:14:34+07:00</t>
+          <t>2026-10-31T05:25:23+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T04:28:18+07:00</t>
+          <t>2026-10-31T05:51:46+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T05:25:23+07:00</t>
+          <t>2026-10-31T06:49:08+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T05:51:46+07:00</t>
+          <t>2026-10-31T07:10:41+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T06:49:08+07:00</t>
+          <t>2026-10-31T07:33:07+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T07:10:41+07:00</t>
+          <t>2026-10-31T08:33:18+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T07:33:07+07:00</t>
+          <t>2026-10-31T09:24:36+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T08:33:18+07:00</t>
+          <t>2026-10-31T09:36:22+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T09:24:36+07:00</t>
+          <t>2026-10-31T11:20:19+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T09:36:22+07:00</t>
+          <t>2026-10-31T11:21:18+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -2874,7 +2874,7 @@
         <v>24947</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>24947</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>27027</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>29237</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T11:20:19+07:00</t>
+          <t>2026-10-31T12:55:37+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T11:21:18+07:00</t>
+          <t>2026-10-31T13:17:12+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1493,7 +1493,7 @@
         <v>42887</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>49127</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>49517</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>50557</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>52767</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>53027</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>62127</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>62127</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>53027</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>55757</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>58877</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>70577</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>72007</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>72397</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>73177</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>27027</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>28327</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>32227</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>25337</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>42887</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H51" s="13" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>49127</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H52" s="13" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>49517</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>50557</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H54" s="13" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>52767</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>53027</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         <v>62127</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>62127</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H58" s="13" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>53027</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>55757</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>58877</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>70577</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>72007</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>72397</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>73177</v>
       </c>
       <c r="G65" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T12:55:37+07:00</t>
+          <t>2026-10-31T14:31:42+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T13:17:12+07:00</t>
+          <t>2026-10-31T14:33:57+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T14:31:42+07:00</t>
+          <t>2026-10-31T16:16:37+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T14:33:57+07:00</t>
+          <t>2026-10-31T16:21:02+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T16:16:37+07:00</t>
+          <t>2026-10-31T17:25:12+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T16:21:02+07:00</t>
+          <t>2026-10-31T17:55:48+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T17:25:12+07:00</t>
+          <t>2026-10-31T18:49:09+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T17:55:48+07:00</t>
+          <t>2026-10-31T19:10:20+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1421,7 +1421,7 @@
         <v>32227</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>35477</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>25207</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>25727</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>26247</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>26637</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>26767</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>27157</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>27417</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="13" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>28197</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>29887</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>27807</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>30407</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" s="13" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>30667</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>31057</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H24" s="13" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>31317</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>31317</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H26" s="13" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>32227</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>32227</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>34177</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>36387</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>29627</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>29887</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>30017</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>40677</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>26767</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H38" s="13" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>27807</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>27807</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>27937</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>27937</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>27937</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>30667</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>30667</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>28847</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>30927</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>32227</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>35477</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H50" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T18:49:09+07:00</t>
+          <t>2026-10-31T20:25:37+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T19:10:20+07:00</t>
+          <t>2026-10-31T20:29:20+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T20:25:37+07:00</t>
+          <t>2026-10-31T21:50:02+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T20:29:20+07:00</t>
+          <t>2026-10-31T22:14:52+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -1385,7 +1385,7 @@
         <v>32617</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>25337</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H36" s="13" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>32617</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T21:50:02+07:00</t>
+          <t>2026-10-31T23:09:44+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T22:14:52+07:00</t>
+          <t>2026-10-31T23:23:40+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T23:09:44+07:00</t>
+          <t>2026-11-01T00:20:55+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-10-31T23:23:40+07:00</t>
+          <t>2026-11-01T00:51:04+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-11-01T00:20:55+07:00</t>
+          <t>2026-11-01T01:58:25+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-11-01T00:51:04+07:00</t>
+          <t>2026-11-01T02:06:46+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-11-01T01:58:25+07:00</t>
+          <t>2026-11-01T03:06:43+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-11-01T02:06:46+07:00</t>
+          <t>2026-11-01T03:31:46+07:00</t>
         </is>
       </c>
     </row>

--- a/redmibook_pro_auto.xlsx
+++ b/redmibook_pro_auto.xlsx
@@ -7712,7 +7712,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2026-11-01T03:06:43+07:00</t>
+          <t>2026-11-01T04:23:45+07:00</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>2026-11-01T03:31:46+07:00</t>
+          <t>2026-11-01T04:50:49+07:00</t>
         </is>
       </c>
     </row>
